--- a/Golden Cala/Scripts/Shoof Integration/Sales Module/Sales Order/Technical Reference.xlsx
+++ b/Golden Cala/Scripts/Shoof Integration/Sales Module/Sales Order/Technical Reference.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetSuiteCompanies\Golden Cala\Scripts\Shoof Integration\Sales Module\Sales Order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F59AAF-7369-471B-B551-63D6195B35E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4E950C-47DC-459D-AFF7-D97FC9C6BAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9045" yWindow="2355" windowWidth="17280" windowHeight="8925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>customscript_vs_sl_shoof_api_so</t>
   </si>
   <si>
-    <t>Custom Recprd</t>
-  </si>
-  <si>
     <t>Payment Method</t>
   </si>
   <si>
@@ -82,6 +79,9 @@
   </si>
   <si>
     <t>Shoof Sales Order</t>
+  </si>
+  <si>
+    <t>Custom Record</t>
   </si>
 </sst>
 </file>
@@ -154,6 +154,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28574</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>42811</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>392835</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>39266</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{500073FF-56D7-7BF3-6C3C-7B62A60BBC86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5486399" y="42811"/>
+          <a:ext cx="8289061" cy="4187455"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,10 +499,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -472,48 +521,49 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>